--- a/outputs/daily/hr_rankings_2026-10-19_full.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-19_full.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1839,24 +1855,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -1864,22 +1880,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,101 +2019,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2115,24 +2135,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -2140,22 +2160,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,62 +2198,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2253,12 +2269,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -2268,12 +2284,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2283,101 +2299,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2391,12 +2415,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2416,12 +2440,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,62 +2478,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2529,12 +2549,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -2544,7 +2564,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2559,67 +2579,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -2652,8 +2672,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2672,7 +2700,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3292,10 +3328,10 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3305,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -3480,8 +3512,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3495,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3520,22 +3560,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,62 +3598,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3633,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,101 +3699,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3771,24 +3815,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -3796,22 +3840,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3909,27 +3949,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,101 +3979,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4352,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,12 +4375,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4348,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4461,12 +4509,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,67 +4539,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4584,8 +4632,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4599,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -4624,22 +4680,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,62 +4718,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4737,27 +4789,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4819,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4900,12 +4960,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,7 +4998,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -4948,10 +5008,10 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -4961,39 +5021,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5136,8 +5192,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,24 +5215,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -5176,22 +5240,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5289,27 +5349,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,101 +5379,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5752,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,12 +6126,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>51.5</v>
+        <v>53.9</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>32</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>50</v>
+        <v>52.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>32</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.7</v>
+        <v>51.2</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>33.4</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S4" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.6</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>33.4</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S5" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7133,24 +7221,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Victor Mesa Jr.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7158,22 +7246,22 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>43.3</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,62 +7284,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>36.3</v>
+        <v>43.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S6" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>10.1</v>
+        <v>54.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7271,27 +7355,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -7301,101 +7385,109 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>32.53</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7409,24 +7501,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -7434,22 +7526,22 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,62 +7564,58 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>36.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>10.1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7547,12 +7635,12 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -7562,12 +7650,12 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7577,101 +7665,109 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7685,12 +7781,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7710,12 +7806,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.3</v>
+        <v>45.9</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,62 +7844,58 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>43.3</v>
+        <v>41</v>
       </c>
       <c r="Q8" t="n">
         <v>32</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>20.9</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7823,12 +7915,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -7838,7 +7930,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -7853,67 +7945,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -7946,8 +8038,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7966,7 +8066,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.5</v>
+        <v>44.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>31.6</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T9" t="n">
         <v>75</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40</v>
+        <v>42.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>31.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S10" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
         <v>75</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.9</v>
+        <v>39.5</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,7 +8684,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -8586,10 +8694,10 @@
         <v>33.4</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S11" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -8599,39 +8707,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -8774,8 +8878,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8789,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -8814,22 +8926,22 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>38</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,62 +8964,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.9</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S12" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>43.1</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8927,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,101 +9065,109 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9065,24 +9181,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9090,22 +9206,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>34.8</v>
+        <v>37.5</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,62 +9244,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>10.6</v>
+        <v>2.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>70.59999999999999</v>
+        <v>43.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9203,27 +9315,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,101 +9345,109 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.3</v>
+        <v>34.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>31.6</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S14" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9718,16 @@
           <t>28.41</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,12 +9741,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>622761</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jorge Mateo</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9642,7 +9766,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.7</v>
+        <v>34.4</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>23.3</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>32</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9755,12 +9875,12 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/16, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,67 +9905,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>35.51</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>98.4476</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1223</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2522</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>31.46</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1044</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9878,8 +9998,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9893,24 +10021,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>690984</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Petey Halpin</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -9918,22 +10046,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Shawn Armstrong</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>542888</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>30.3</v>
+        <v>34.3</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,62 +10084,58 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>10.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>33.4</v>
+        <v>32</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S16" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>38.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10031,27 +10155,27 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Contact streak: 3/8 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10185,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>81.45</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>93.4449</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3143</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0924</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2902</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.15</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0707</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>35.04</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.35</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.3695</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.1577</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>28.41</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>29.92</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10194,12 +10326,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>29.9</v>
+        <v>33.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,7 +10364,7 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
@@ -10242,10 +10374,10 @@
         <v>32</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
@@ -10255,39 +10387,35 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10430,8 +10558,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,24 +10581,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>663743</t>
+          <t>690984</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Nick Fortes</t>
+          <t>Petey Halpin</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-20T00:08:00Z</t>
@@ -10470,22 +10606,22 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Shawn Armstrong</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>542888</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>29.8</v>
+        <v>32.9</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>12.8</v>
+        <v>7</v>
       </c>
       <c r="Q18" t="n">
-        <v>32</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>18.3</v>
+        <v>38.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10583,27 +10715,27 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 1 HR</t>
+          <t>Contact streak: 3/8 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,101 +10745,109 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>17.85</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.03</t>
+          <t>81.45</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.0812</t>
+          <t>93.4449</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3248</t>
+          <t>0.3143</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.093</t>
+          <t>0.0924</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2721</t>
+          <t>0.2902</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>72.49</t>
+          <t>70.15</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.84</t>
+          <t>40.34</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>18.36</t>
+          <t>31.02</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.0707</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.04</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.35</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3695</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1577</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+          <t>28.41</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>27.3</v>
+        <v>29.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>31.5</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.6</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11118,16 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
